--- a/谱图/报告解析/称量记录1.xlsx
+++ b/谱图/报告解析/称量记录1.xlsx
@@ -1,11 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CC7DDDD-49B6-42F7-AA18-810EF4B91DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1808" yWindow="1808" windowWidth="16199" windowHeight="9307" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5505" yWindow="-13065" windowWidth="23250" windowHeight="12450"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -31,17 +30,21 @@
     <t>试样描述</t>
   </si>
   <si>
-    <t>包材</t>
+    <t>TS26072901001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>TS26073107001</t>
+    <t>混测电子元器件</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="0.0000"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -78,12 +81,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -102,9 +106,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -142,7 +146,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -214,7 +218,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -387,17 +391,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D42"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D81"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.46484375" customWidth="1"/>
-    <col min="2" max="2" width="16.73046875" customWidth="1"/>
+    <col min="1" max="1" width="12.5" customWidth="1"/>
+    <col min="2" max="2" width="16.75" customWidth="1"/>
     <col min="3" max="3" width="17" customWidth="1"/>
-    <col min="4" max="4" width="9.73046875" customWidth="1"/>
+    <col min="4" max="4" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -411,216 +415,413 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="1">
-        <v>46232</v>
+        <v>46238</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>4</v>
+      <c r="D2" s="3">
+        <v>0.50880000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="1"/>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D3" s="3"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="1"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D4" s="3"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="1"/>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D5" s="3"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="1"/>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="1"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="1"/>
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="1"/>
       <c r="B9" s="2"/>
       <c r="C9" s="2"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="1"/>
       <c r="B10" s="2"/>
       <c r="C10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="1"/>
       <c r="B11" s="2"/>
       <c r="C11" s="2"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" s="1"/>
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" s="1"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="1"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="1"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" s="1"/>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A17" s="1"/>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A18" s="1"/>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A19" s="1"/>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A20" s="1"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:3" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A21" s="1"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A22" s="1"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A23" s="1"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A24" s="1"/>
       <c r="B24" s="2"/>
       <c r="C24" s="2"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A25" s="1"/>
       <c r="B25" s="2"/>
       <c r="C25" s="2"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A26" s="1"/>
       <c r="B26" s="2"/>
       <c r="C26" s="2"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A27" s="1"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A28" s="1"/>
       <c r="B28" s="2"/>
       <c r="C28" s="2"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A29" s="1"/>
       <c r="B29" s="2"/>
       <c r="C29" s="2"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A30" s="1"/>
       <c r="B30" s="2"/>
       <c r="C30" s="2"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A31" s="1"/>
       <c r="B31" s="2"/>
       <c r="C31" s="2"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A32" s="1"/>
       <c r="B32" s="2"/>
       <c r="C32" s="2"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A33" s="1"/>
       <c r="B33" s="2"/>
       <c r="C33" s="2"/>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A34" s="1"/>
       <c r="B34" s="2"/>
       <c r="C34" s="2"/>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A35" s="1"/>
       <c r="B35" s="2"/>
       <c r="C35" s="2"/>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A36" s="1"/>
       <c r="B36" s="2"/>
       <c r="C36" s="2"/>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A37" s="1"/>
       <c r="B37" s="2"/>
       <c r="C37" s="2"/>
     </row>
-    <row r="38" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A38" s="1"/>
       <c r="B38" s="2"/>
       <c r="C38" s="2"/>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A39" s="1"/>
       <c r="B39" s="2"/>
       <c r="C39" s="2"/>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A40" s="1"/>
       <c r="B40" s="2"/>
       <c r="C40" s="2"/>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A41" s="1"/>
       <c r="B41" s="2"/>
       <c r="C41" s="2"/>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.15">
       <c r="A42" s="1"/>
       <c r="B42" s="2"/>
       <c r="C42" s="2"/>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A43" s="1"/>
+      <c r="B43" s="2"/>
+      <c r="C43" s="2"/>
+    </row>
+    <row r="44" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A44" s="1"/>
+      <c r="B44" s="2"/>
+      <c r="C44" s="2"/>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A45" s="1"/>
+      <c r="B45" s="2"/>
+      <c r="C45" s="2"/>
+    </row>
+    <row r="46" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A46" s="1"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A47" s="1"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+    </row>
+    <row r="48" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A48" s="1"/>
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+    </row>
+    <row r="49" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A49" s="1"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+    </row>
+    <row r="50" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A50" s="1"/>
+      <c r="B50" s="2"/>
+      <c r="C50" s="2"/>
+    </row>
+    <row r="51" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A51" s="1"/>
+      <c r="B51" s="2"/>
+      <c r="C51" s="2"/>
+    </row>
+    <row r="52" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A52" s="1"/>
+      <c r="B52" s="2"/>
+      <c r="C52" s="2"/>
+    </row>
+    <row r="53" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A53" s="1"/>
+      <c r="B53" s="2"/>
+      <c r="C53" s="2"/>
+    </row>
+    <row r="54" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A54" s="1"/>
+      <c r="B54" s="2"/>
+      <c r="C54" s="2"/>
+    </row>
+    <row r="55" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A55" s="1"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+    </row>
+    <row r="56" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A56" s="1"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+    </row>
+    <row r="57" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A57" s="1"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+    </row>
+    <row r="58" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A58" s="1"/>
+      <c r="B58" s="2"/>
+      <c r="C58" s="2"/>
+    </row>
+    <row r="59" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A59" s="1"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+    </row>
+    <row r="60" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A60" s="1"/>
+      <c r="B60" s="2"/>
+      <c r="C60" s="2"/>
+    </row>
+    <row r="61" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A61" s="1"/>
+      <c r="B61" s="2"/>
+      <c r="C61" s="2"/>
+    </row>
+    <row r="62" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A62" s="1"/>
+      <c r="B62" s="2"/>
+      <c r="C62" s="2"/>
+    </row>
+    <row r="63" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A63" s="1"/>
+      <c r="B63" s="2"/>
+      <c r="C63" s="2"/>
+    </row>
+    <row r="64" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A64" s="1"/>
+      <c r="B64" s="2"/>
+      <c r="C64" s="2"/>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A65" s="1"/>
+      <c r="B65" s="2"/>
+      <c r="C65" s="2"/>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A66" s="1"/>
+      <c r="B66" s="2"/>
+      <c r="C66" s="2"/>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A67" s="1"/>
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A68" s="1"/>
+      <c r="B68" s="2"/>
+      <c r="C68" s="2"/>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A69" s="1"/>
+      <c r="B69" s="2"/>
+      <c r="C69" s="2"/>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A70" s="1"/>
+      <c r="B70" s="2"/>
+      <c r="C70" s="2"/>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A71" s="1"/>
+      <c r="B71" s="2"/>
+      <c r="C71" s="2"/>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A72" s="1"/>
+      <c r="B72" s="2"/>
+      <c r="C72" s="2"/>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A73" s="1"/>
+      <c r="B73" s="2"/>
+      <c r="C73" s="2"/>
+    </row>
+    <row r="74" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A74" s="1"/>
+      <c r="B74" s="2"/>
+      <c r="C74" s="2"/>
+    </row>
+    <row r="75" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A75" s="1"/>
+      <c r="B75" s="2"/>
+      <c r="C75" s="2"/>
+    </row>
+    <row r="77" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A77" s="1"/>
+      <c r="B77" s="2"/>
+      <c r="C77" s="2"/>
+    </row>
+    <row r="78" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A78" s="1"/>
+      <c r="B78" s="2"/>
+      <c r="C78" s="2"/>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A79" s="1"/>
+      <c r="B79" s="2"/>
+      <c r="C79" s="2"/>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A80" s="1"/>
+      <c r="B80" s="2"/>
+      <c r="C80" s="2"/>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A81" s="1"/>
+      <c r="B81" s="2"/>
+      <c r="C81" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -630,9 +831,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -640,9 +841,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
